--- a/monitoring_forms/042_incident_monitoring_form--monitoring_forms.xlsx
+++ b/monitoring_forms/042_incident_monitoring_form--monitoring_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1033,8 +1033,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'resolved'}</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Resolved'}</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'type_1'}</t>
+          <t>type_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Type 1'}</t>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'type_2'}</t>
+          <t>type_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Type 2'}</t>
+          <t>Type 2</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'type_3'}</t>
+          <t>type_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Type 3'}</t>
+          <t>Type 3</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_reviewed'}</t>
+          <t>not_reviewed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not Reviewed'}</t>
+          <t>Not Reviewed</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'reviewed'}</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Reviewed'}</t>
+          <t>Reviewed</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'user_1'}</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'User 1'}</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'user_2'}</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'User 2'}</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'user_1'}</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'User 1'}</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'user_2'}</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'User 2'}</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'user_1'}</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'User 1'}</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'user_2'}</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'User 2'}</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
